--- a/inst/resources/variable_schema_data_household_template.xlsx
+++ b/inst/resources/variable_schema_data_household_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55CEBCC-DAE6-4B7B-82F3-DAE0041B6E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F0A035-265A-493E-88C9-D85B0F3D2917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9675" uniqueCount="2075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9678" uniqueCount="2076">
   <si>
     <t>rule_type</t>
   </si>
@@ -6245,6 +6245,9 @@
   </si>
   <si>
     <t>acceptable,⧫Acceptable⧫</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -6868,6 +6871,9 @@
       <c r="R2" t="s">
         <v>25</v>
       </c>
+      <c r="S2" t="s">
+        <v>2075</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -6897,6 +6903,9 @@
       <c r="N3" t="s">
         <v>30</v>
       </c>
+      <c r="S3" t="s">
+        <v>2075</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -6925,6 +6934,9 @@
       </c>
       <c r="N4" t="s">
         <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>2075</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
